--- a/dev/StructureDefinition-bc-location.xlsx
+++ b/dev/StructureDefinition-bc-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2708,7 +2708,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>150</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>155</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>160</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>170</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>194</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>208</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>213</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>218</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>228</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>233</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>254</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>260</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>267</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>330</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>343</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>349</v>
       </c>
@@ -8332,12 +8332,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL62">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
